--- a/data/trans_orig/P16A04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A04-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14277</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>20696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29541</t>
+          <t>29066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>678717</t>
+          <t>678827</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>689258</t>
+          <t>689322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>668394</t>
+          <t>667655</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>681923</t>
+          <t>682074</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1351804</t>
+          <t>1352279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1369334</t>
+          <t>1368932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37762</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29419</t>
+          <t>29492</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>30822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60544</t>
+          <t>58314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>924038</t>
+          <t>923085</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>945726</t>
+          <t>945791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>938974</t>
+          <t>938901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>957622</t>
+          <t>957906</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1869649</t>
+          <t>1871879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1898829</t>
+          <t>1899371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35361</t>
+          <t>36440</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>24930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47479</t>
+          <t>47820</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661910</t>
+          <t>661808</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673860</t>
+          <t>673845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>648480</t>
+          <t>647401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>667780</t>
+          <t>666896</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1314871</t>
+          <t>1314530</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1336593</t>
+          <t>1337420</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26402</t>
+          <t>26732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>30867</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48673</t>
+          <t>50775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915820</t>
+          <t>915490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931954</t>
+          <t>931738</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1008631</t>
+          <t>1007745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1026564</t>
+          <t>1026489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1932161</t>
+          <t>1930059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1955381</t>
+          <t>1954356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45782</t>
+          <t>45311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74568</t>
+          <t>75059</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58066</t>
+          <t>59272</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93580</t>
+          <t>93543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112047</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158487</t>
+          <t>155307</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3200957</t>
+          <t>3200466</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3229743</t>
+          <t>3230214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3285617</t>
+          <t>3285654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3321131</t>
+          <t>3319925</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6496235</t>
+          <t>6499415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6542675</t>
+          <t>6542531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>39125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33245</t>
+          <t>32917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63009</t>
+          <t>62798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>660856</t>
+          <t>661639</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>684494</t>
+          <t>684525</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>662503</t>
+          <t>662372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>681270</t>
+          <t>680941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1331106</t>
+          <t>1331317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1360870</t>
+          <t>1361198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>20419</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46589</t>
+          <t>47129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>30742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58711</t>
+          <t>57864</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57984</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95360</t>
+          <t>93399</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>969167</t>
+          <t>968627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>994442</t>
+          <t>995337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>969108</t>
+          <t>969955</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>996445</t>
+          <t>997077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1948215</t>
+          <t>1950176</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1985591</t>
+          <t>1986179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>33128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>20342</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22841</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>45841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>723577</t>
+          <t>723410</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>743662</t>
+          <t>743167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>756557</t>
+          <t>755941</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>771063</t>
+          <t>770849</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1485312</t>
+          <t>1486980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1509980</t>
+          <t>1511234</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30560</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37804</t>
+          <t>38348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32498</t>
+          <t>33403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62151</t>
+          <t>60870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912486</t>
+          <t>912884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932103</t>
+          <t>932646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1010959</t>
+          <t>1010415</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1031060</t>
+          <t>1030606</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1929658</t>
+          <t>1930939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1959311</t>
+          <t>1958406</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73191</t>
+          <t>76700</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118752</t>
+          <t>118937</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83466</t>
+          <t>80717</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124986</t>
+          <t>122792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168636</t>
+          <t>168871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229140</t>
+          <t>228183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3297351</t>
+          <t>3297166</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3342912</t>
+          <t>3339403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3421231</t>
+          <t>3423425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3462751</t>
+          <t>3465500</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6733180</t>
+          <t>6734137</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6793684</t>
+          <t>6793449</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24330</t>
+          <t>23564</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39807</t>
+          <t>40190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>652054</t>
+          <t>653135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668762</t>
+          <t>667913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>648509</t>
+          <t>649275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663612</t>
+          <t>664029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1307832</t>
+          <t>1307449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1328591</t>
+          <t>1329513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29746</t>
+          <t>29492</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36301</t>
+          <t>34822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>30491</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57923</t>
+          <t>56179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>992685</t>
+          <t>992939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1010520</t>
+          <t>1009899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1006612</t>
+          <t>1008091</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1027291</t>
+          <t>1028332</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2007421</t>
+          <t>2009165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2033570</t>
+          <t>2034853</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>18725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>741684</t>
+          <t>740827</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>755371</t>
+          <t>754341</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>759369</t>
+          <t>759179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>777060</t>
+          <t>777266</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1507556</t>
+          <t>1507384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1528868</t>
+          <t>1529088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>18451</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39288</t>
+          <t>39051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>17542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40609</t>
+          <t>40587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41446</t>
+          <t>39966</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71202</t>
+          <t>70813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>898279</t>
+          <t>898516</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>919199</t>
+          <t>919116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1003170</t>
+          <t>1003192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1025797</t>
+          <t>1026237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1910144</t>
+          <t>1910533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1939900</t>
+          <t>1941380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53948</t>
+          <t>53214</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87983</t>
+          <t>86710</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>63836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102289</t>
+          <t>101231</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124314</t>
+          <t>126017</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>177422</t>
+          <t>177249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3306367</t>
+          <t>3307640</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3340402</t>
+          <t>3341136</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3442253</t>
+          <t>3443311</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3481115</t>
+          <t>3480706</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6761470</t>
+          <t>6761643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6814578</t>
+          <t>6812875</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22236</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20950</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38309</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>614472</t>
+          <t>614535</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>628012</t>
+          <t>628194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653186</t>
+          <t>653107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>664345</t>
+          <t>664210</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1272064</t>
+          <t>1271395</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1289416</t>
+          <t>1289423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>35074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22151</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39759</t>
+          <t>39668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32750</t>
+          <t>32375</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66844</t>
+          <t>65782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1158569</t>
+          <t>1157790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1183507</t>
+          <t>1183339</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>918347</t>
+          <t>918438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>935955</t>
+          <t>936096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2084127</t>
+          <t>2085189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2118221</t>
+          <t>2118596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29391</t>
+          <t>29201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>34673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>24954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55299</t>
+          <t>55135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>674293</t>
+          <t>674483</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>693947</t>
+          <t>693742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>899475</t>
+          <t>898127</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>923086</t>
+          <t>921763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1581185</t>
+          <t>1581349</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1611458</t>
+          <t>1611530</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36806</t>
+          <t>35974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31664</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66241</t>
+          <t>63766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54264</t>
+          <t>53089</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93493</t>
+          <t>89238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>890025</t>
+          <t>890857</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>910172</t>
+          <t>909704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025133</t>
+          <t>1027608</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1059710</t>
+          <t>1058580</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1924712</t>
+          <t>1928967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1963941</t>
+          <t>1965116</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56889</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97638</t>
+          <t>97118</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88403</t>
+          <t>91030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>136558</t>
+          <t>136067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>157336</t>
+          <t>154438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>219395</t>
+          <t>216564</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3360692</t>
+          <t>3361212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3401441</t>
+          <t>3404325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3521144</t>
+          <t>3521635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3569299</t>
+          <t>3566672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6896637</t>
+          <t>6899468</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6958696</t>
+          <t>6961594</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A04-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14167</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20696</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>29416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>678827</t>
+          <t>678704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>689322</t>
+          <t>689212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>667655</t>
+          <t>669049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>682074</t>
+          <t>682409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1352279</t>
+          <t>1351929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1368932</t>
+          <t>1369114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>37195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29492</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58314</t>
+          <t>57454</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>923085</t>
+          <t>924605</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>945791</t>
+          <t>946160</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>938901</t>
+          <t>938759</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>957906</t>
+          <t>957369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1871879</t>
+          <t>1872739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1899371</t>
+          <t>1899766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>16186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36440</t>
+          <t>36206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24930</t>
+          <t>23658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47820</t>
+          <t>47310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661808</t>
+          <t>662323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673845</t>
+          <t>673734</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647401</t>
+          <t>647635</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>666896</t>
+          <t>667286</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1314530</t>
+          <t>1315040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1337420</t>
+          <t>1338692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26732</t>
+          <t>26573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30867</t>
+          <t>29153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26478</t>
+          <t>26513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50775</t>
+          <t>50662</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915490</t>
+          <t>915649</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931738</t>
+          <t>931637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007745</t>
+          <t>1009459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1026489</t>
+          <t>1026758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1930059</t>
+          <t>1930172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1954356</t>
+          <t>1954321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>45808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75059</t>
+          <t>76703</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>57529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93543</t>
+          <t>93713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112191</t>
+          <t>112708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155307</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3200466</t>
+          <t>3198822</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3230214</t>
+          <t>3229717</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3285654</t>
+          <t>3285484</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3319925</t>
+          <t>3321668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6499415</t>
+          <t>6495438</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6542531</t>
+          <t>6542014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16239</t>
+          <t>16296</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39125</t>
+          <t>39031</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12410</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>30547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32917</t>
+          <t>33748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62798</t>
+          <t>62742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661639</t>
+          <t>661733</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>684525</t>
+          <t>684468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>662372</t>
+          <t>662804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>680941</t>
+          <t>680453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1331317</t>
+          <t>1331373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1361198</t>
+          <t>1360367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20419</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47129</t>
+          <t>46690</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>31661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57864</t>
+          <t>60409</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57396</t>
+          <t>59097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93399</t>
+          <t>95265</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>968627</t>
+          <t>969066</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>995337</t>
+          <t>994927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>969955</t>
+          <t>967410</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>997077</t>
+          <t>996158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1950176</t>
+          <t>1948310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1986179</t>
+          <t>1984478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33128</t>
+          <t>32414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>22245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45841</t>
+          <t>46472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>723410</t>
+          <t>724124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>743167</t>
+          <t>743191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>755941</t>
+          <t>755661</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770849</t>
+          <t>770518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1486980</t>
+          <t>1486349</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1511234</t>
+          <t>1510576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>38871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33403</t>
+          <t>33384</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60870</t>
+          <t>60366</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912884</t>
+          <t>914127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932646</t>
+          <t>933261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1010415</t>
+          <t>1009892</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1030606</t>
+          <t>1030331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1930939</t>
+          <t>1931443</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1958406</t>
+          <t>1958425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>77743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118937</t>
+          <t>121968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80717</t>
+          <t>83879</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122792</t>
+          <t>124616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168871</t>
+          <t>168997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228183</t>
+          <t>230362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3297166</t>
+          <t>3294135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3339403</t>
+          <t>3338360</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3423425</t>
+          <t>3421601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3465500</t>
+          <t>3462338</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6734137</t>
+          <t>6731958</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6793449</t>
+          <t>6793323</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23564</t>
+          <t>23911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40190</t>
+          <t>39848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>653135</t>
+          <t>653736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>667913</t>
+          <t>668072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649275</t>
+          <t>648928</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>664029</t>
+          <t>664170</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1307449</t>
+          <t>1307791</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1329513</t>
+          <t>1329238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29492</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34822</t>
+          <t>33927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30491</t>
+          <t>31423</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56179</t>
+          <t>56949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>992939</t>
+          <t>990899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1009899</t>
+          <t>1009566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1008091</t>
+          <t>1008986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1028332</t>
+          <t>1028126</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2009165</t>
+          <t>2008395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2034853</t>
+          <t>2033921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18725</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37179</t>
+          <t>36688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740827</t>
+          <t>740174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754341</t>
+          <t>754473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>759179</t>
+          <t>755946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>777266</t>
+          <t>776647</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1507384</t>
+          <t>1507875</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1529088</t>
+          <t>1528990</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39051</t>
+          <t>39266</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17542</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40587</t>
+          <t>39220</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39966</t>
+          <t>40012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70813</t>
+          <t>70283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>898516</t>
+          <t>898301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>919116</t>
+          <t>919276</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1003192</t>
+          <t>1004559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1026237</t>
+          <t>1026085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1910533</t>
+          <t>1911063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1941380</t>
+          <t>1941334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53214</t>
+          <t>54463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86710</t>
+          <t>88587</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63836</t>
+          <t>63356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101231</t>
+          <t>101368</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126017</t>
+          <t>126736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>177249</t>
+          <t>179493</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3307640</t>
+          <t>3305763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3341136</t>
+          <t>3339887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3443311</t>
+          <t>3443174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3480706</t>
+          <t>3481186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6761643</t>
+          <t>6759399</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6812875</t>
+          <t>6812156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>24172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>11689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22315</t>
+          <t>24387</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,27 +6639,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>30784</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20950</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38978</t>
+          <t>42233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>622686</t>
+          <t>676589</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>614535</t>
+          <t>666043</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>628194</t>
+          <t>682786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>659517</t>
+          <t>715625</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653107</t>
+          <t>708395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>664210</t>
+          <t>721093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,22 +6752,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1282204</t>
+          <t>1392213</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1271395</t>
+          <t>1380764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1289423</t>
+          <t>1399750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>23341</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>14799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35074</t>
+          <t>37288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29190</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22010</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39668</t>
+          <t>41357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>50150</t>
+          <t>54703</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32375</t>
+          <t>41693</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65782</t>
+          <t>71678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1171904</t>
+          <t>1025576</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1157790</t>
+          <t>1011629</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1183339</t>
+          <t>1034118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>928916</t>
+          <t>1039477</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>918438</t>
+          <t>1029481</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>936096</t>
+          <t>1048303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2100821</t>
+          <t>2065052</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2085189</t>
+          <t>2048077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2118596</t>
+          <t>2078062</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29201</t>
+          <t>34261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>28106</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34673</t>
+          <t>38809</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39068</t>
+          <t>48176</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24954</t>
+          <t>35573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55135</t>
+          <t>63892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>686622</t>
+          <t>782016</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>674483</t>
+          <t>767825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>693742</t>
+          <t>790294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>910794</t>
+          <t>783557</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>898127</t>
+          <t>772854</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>921763</t>
+          <t>791907</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1597416</t>
+          <t>1565572</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1581349</t>
+          <t>1549856</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1611530</t>
+          <t>1578175</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>25109</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17127</t>
+          <t>16435</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35974</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44556</t>
+          <t>47518</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32794</t>
+          <t>36985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63766</t>
+          <t>61401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>69465</t>
+          <t>72627</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53089</t>
+          <t>58719</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89238</t>
+          <t>88848</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>901923</t>
+          <t>964953</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>890857</t>
+          <t>953779</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>909704</t>
+          <t>973627</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1046818</t>
+          <t>1069513</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1027608</t>
+          <t>1055630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1058580</t>
+          <t>1080046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1948740</t>
+          <t>2034466</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1928967</t>
+          <t>2018245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1965116</t>
+          <t>2048374</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>75194</t>
+          <t>82148</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54005</t>
+          <t>64087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97118</t>
+          <t>104513</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>124142</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91030</t>
+          <t>105311</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>136067</t>
+          <t>144065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>186852</t>
+          <t>206290</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>154438</t>
+          <t>182214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>216564</t>
+          <t>236764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3383136</t>
+          <t>3449132</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3361212</t>
+          <t>3426767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3404325</t>
+          <t>3467193</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3546045</t>
+          <t>3608171</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3521635</t>
+          <t>3588248</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3566672</t>
+          <t>3627002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6929180</t>
+          <t>7057303</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6899468</t>
+          <t>7026829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6961594</t>
+          <t>7081379</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
